--- a/f2_tabelas/tabela_obitos_por_ano.xlsx
+++ b/f2_tabelas/tabela_obitos_por_ano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -462,6 +462,14 @@
         <v>3888</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14">
+        <v>2024</v>
+      </c>
+      <c r="B14">
+        <v>3362</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
